--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -20,6 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_동선_스파게티" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_전력측정" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_인터뷰" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_배치추적" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_WIP센서스" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_게이트카운트" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_의사결정규칙" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_워크샘플링" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_검증지표" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1149,6 +1155,606 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>아침 투입 주문 2~3개를 끝까지 따라가며 공정마다 1행. 리드타임·라우팅·대기의 1차 ground truth (검증 전용, 모델 입력 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>배치번호(스티커)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>주문/제품ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>공정/기계ID</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>도착 시각</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>착수 시각</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>완료 시각</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>출발 시각</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>대기 사유(기계 바쁨/운반/자재/셋업/사람 없음)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>운반 수단</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>사진 파일</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>하루 2~3회 전 구역을 돌며 기록. Little's law 검증과 버퍼 용량 추정용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>회차(09/13/16시)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>시각</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>구역/기계ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>대차 수</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>팔레트/바닥 적치 수</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>부품 수(추정)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>제품ID</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>대기 사유</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>사진</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>통로 교차점 3~5개. 카메라가 있으면 영상에서 사후 집계. 흐름 from-to 행렬 검증용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>게이트ID(교차점)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>시작 시각</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>종료 시각(30분)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>대차 통과(적재)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>대차 통과(공차)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>지게차 통과</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>보행 통과</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>반장·사장 인터뷰에서 '만약 ~면 ~한다' 형식으로 받아 적는다. 이 시트가 비어 있으면 모델은 '이상 공장'이 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>주제(배치구성/투입/기계선택/셋업시점/운반/잔업/급한주문/조립착수/품질판정/인력대체)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>만약 (조건)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>그러면 (행동)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>말한 사람</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>모델 반영(규칙 코드)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>13:00~15:00 3분 간격, 전 작업자. 가동률·재배치 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>시각</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>작업자ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>상태(가공/핸들링/보행/대기/셋업/부재)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>위치(기계ID)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>대기 사유</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>03_공장복제_명세서 §1.2. 입력에 쓰지 않은 데이터로만 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>실제 값</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>허용 오차</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>모델 값</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>차이</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>일/주 출하량(제품별)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>출하일지</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>±10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>추적 배치 리드타임</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13_배치추적</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>±15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>시각별 구역 WIP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14_WIP센서스</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>±20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>기계별 가동률</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CT 로그/워크샘플링</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>±10%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>병목 앞 평균 대기열</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>센서스/영상</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>순위 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>게이트별 시간당 통과</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15_게이트카운트</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>±20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>일 kWh / 최대수요 kW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>고지서/파워플래너</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>±10% / ±15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>셋업 횟수/일</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>반장 기록</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>±1회</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -26,6 +26,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_의사결정규칙" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_워크샘플링" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_검증지표" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_제약대장" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_외주경로" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_from-to" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_REL관계도" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1828,13 +1832,311 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기계를 '못 옮기는 진짜 이유'. 집진 메인 덕트 경로·드롭 지름, 공압 링메인·드롭, 3상 드롭, 바닥 하중·피트, 독 높이·문 폭, 피난 통로, 도장부스 방폭 구역, 덕트 아래 유효 천장고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>제약ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>종류(집진덕트/공압배관/분전반/바닥하중/피트·기초/독·문/소방피난/부스방폭/크레인/기둥/천장고)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>위치 x</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>위치 y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>범위·치수(지름 mm, 폭 m, 높이 m)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>연결 기계ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>이동 가능(Y/N)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>이전 비용(만원, 추정)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>근거(사진/설비담당)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>도어·상판·철재·유리는 외주 병렬 경로. 외주 입고 대기가 출하를 막는 경우를 모델에 넣기 위한 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>외주 품목(도어/상판/철재/유리/도장)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>외주처</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>발주 시점(어느 공정 후·시공일 D-n)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>리드타임 min(일)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>합류 지점(조립/포장/시공현장)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>지연 시 조치(몸통 어디 적치)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>월 건수</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>지연 빈도(회/월)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>흐름 행렬. 기록 수량 × 관찰 라우팅 → 대차 단위. 거리는 직선이 아니라 통로 경로. 아래쪽 삼각 = 역류(backtracking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>From(구역/기계ID)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>To(구역/기계ID)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>대차/팔레트 이동 수(일)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>운반 수단</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>통로 거리(m, 통로 따라)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SLP 활동관계도. X(격리)는 집진·도장부스·소음. A와 X는 각 5% 이내, U는 50% 안팎</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>활동 i</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>활동 j</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>근접도(A/E/I/O/U/X)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>이유코드(1흐름/2감독/3인원/4접촉/5편의/6공용설비/7서류/8소음·분진·화재/9서비스)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>말한 사람/관찰</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2009,80 +2311,120 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
+          <t>투입측 판재 공간(m)</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>배출측 판재 공간(m)</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>작업자 위치(앞/뒤/옆)</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>이동 등급(A자유/B리깅/C고정)</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>이전 비용(만원, 추정)</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>처리 가능 범위(최대 판 치수·두께)</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>소정지 빈도(회/시간)</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>예열/청소 시간(분/일)</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
           <t>입력버퍼 x</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>입력버퍼 y</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>출력버퍼 x</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>출력버퍼 y</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>버퍼 용량(배치/대차 수)</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>셋업 시간(분)</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>셋업 트리거(색상/두께/제품)</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>MTBF(시간)</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>MTTR(분)</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>불량률(%)</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>명판사진 파일</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>전체사진 파일</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>HMI 사진</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>PLC/HMI 브랜드</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>네트워크 포트(Y/N)</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>

--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -16,20 +16,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_작업자" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_제품_BOM" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_주문이력" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_WIP_스냅샷" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_동선_스파게티" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_전력측정" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_인터뷰" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_배치추적" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_WIP센서스" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_게이트카운트" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_의사결정규칙" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_워크샘플링" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_검증지표" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_제약대장" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_외주경로" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_from-to" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_REL관계도" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_동선_스파게티" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_전력측정" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_인터뷰" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_배치추적" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_WIP센서스" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_게이트카운트" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_의사결정규칙" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_워크샘플링" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_검증지표" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_제약대장" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_외주경로" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_from-to" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_REL관계도" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_운반_출하대장" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -746,52 +746,70 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>하루 2~3회(09:00/13:00/16:00) 공장 전체를 돌며 적치 현황 기록 → Little's law 검증</t>
+          <t>한 명/한 대차를 20~30분 따라가며 기록. 영상 추적(YOLO) 결과도 같은 형식으로 저장</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>시각</t>
+          <t>추적대상(작업자ID/대차/지게차/배치)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>위치(구역/기계ID)</t>
+          <t>시작 시각</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>대차/팔레트 수</t>
+          <t>종료 시각</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>부품 수(추정)</t>
+          <t>출발 위치</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>제품ID</t>
+          <t>도착 위치</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>대기 사유(기계 바쁨/운반 대기/자재 대기/건조)</t>
+          <t>경유 좌표 (x,y;x,y;...)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>거리(m, 추정)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>적재(Y/N)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>적재 부품 수</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -827,59 +845,59 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>한 명/한 대차를 20~30분 따라가며 기록. 영상 추적(YOLO) 결과도 같은 형식으로 저장</t>
+          <t>kW ≈ √3 × V × A × PF / 1000. 한전 파워플래너 15분 데이터는 별도 CSV</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>추적대상(작업자ID/대차/지게차/배치)</t>
+          <t>시각</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>시작 시각</t>
+          <t>측정 대상(기계ID/분전반/인입)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>종료 시각</t>
+          <t>상태(정지/공회전/가공)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>출발 위치</t>
+          <t>전압 V</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>도착 위치</t>
+          <t>전류 A (R)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>경유 좌표 (x,y;x,y;...)</t>
+          <t>A (S)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>거리(m, 추정)</t>
+          <t>A (T)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>적재(Y/N)</t>
+          <t>역률(추정)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>적재 부품 수</t>
+          <t>kW(계산)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>측정자</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -899,83 +917,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>kW ≈ √3 × V × A × PF / 1000. 한전 파워플래너 15분 데이터는 별도 CSV</t>
+          <t>병목·납기·비용·투자 계획·인력 애로. '올해 가장 비쌌던 비용은?' '납기 못 맞춘 횟수와 손해는?' '사고 싶은 기계와 망설이는 이유는?'</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>시각</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>측정 대상(기계ID/분전반/인입)</t>
+          <t>답변(사장/반장)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>상태(정지/공회전/가공)</t>
+          <t>수치</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>전압 V</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>전류 A (R)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>A (S)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>A (T)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>역률(추정)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>kW(계산)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>측정자</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>후속 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【필수】 오늘이 평소와 어떻게 다른가 (투입 예정 현장 수, 결근, 고장, 급한 건, 월말)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【필수】 당일 투입 현장 수 / 당일 출하 현장 수 (처리량 검증: 출하 = 투입 − ΔWIP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>실측 → 도면 → 재단표 작성까지 보통 며칠? 누가? 도면 대기 건수?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>탑차 수, 시공팀 수, 하루 시공 가능 현장 수, 상차 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>시공일이 바뀌거나 취소되는 일이 한 달에 몇 번? 현장에서 불량 발견해 급히 재제작하는 일은?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>주력 제품군과 월 생산량</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>주문 방식(수주/재고), 평균 리드타임</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>공정 순서와 병목(왜)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>기계별 하루 가동시간/잔업/특근</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>가장 자주 바뀌는 세팅과 교체 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WIP 적치 위치와 대차/랙 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>지게차/대차 대수, 경로, 하루 이동 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>불량/재작업 비율과 원인</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>집진기/컴프레서 가동 패턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>월 전기요금, 계약전력, 피크</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ERP/MES/엑셀 기록 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>안전/촬영 금지 구역</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>향후 설비/레이아웃 변경 계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>작업자 수, 숙련 구분, 외국인 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>올해 가장 비쌌던 비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>납기 지연 횟수와 손해</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>사고 싶은 기계와 망설이는 이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>정부 스마트공장 사업 수혜 이력</t>
         </is>
       </c>
     </row>
@@ -990,182 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>병목·납기·비용·투자 계획·인력 애로. '올해 가장 비쌌던 비용은?' '납기 못 맞춘 횟수와 손해는?' '사고 싶은 기계와 망설이는 이유는?'</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>질문</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>답변(사장/반장)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>후속 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>주력 제품군과 월 생산량</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>주문 방식(수주/재고), 평균 리드타임</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>공정 순서와 병목(왜)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>기계별 하루 가동시간/잔업/특근</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>가장 자주 바뀌는 세팅과 교체 시간</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WIP 적치 위치와 대차/랙 수</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>지게차/대차 대수, 경로, 하루 이동 횟수</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>불량/재작업 비율과 원인</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>집진기/컴프레서 가동 패턴</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>월 전기요금, 계약전력, 피크</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ERP/MES/엑셀 기록 형식</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>안전/촬영 금지 구역</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>향후 설비/레이아웃 변경 계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>작업자 수, 숙련 구분, 외국인 비율</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>올해 가장 비쌌던 비용</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>납기 지연 횟수와 손해</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>사고 싶은 기계와 망설이는 이유</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>정부 스마트공장 사업 수혜 이력</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1181,12 +1143,13 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>아침 투입 주문 2~3개를 끝까지 따라가며 공정마다 1행. 리드타임·라우팅·대기의 1차 ground truth (검증 전용, 모델 입력 아님)</t>
+          <t>【검증 전용】 당일: 아침 투입 주문 2~3개를 대차 부착 양식으로 작업자가 직접 기록(관찰자는 2시간마다 확인). 2주간: 같은 양식을 전 배치에 적용 → 생산 리드타임(투입→포장 완료)·셋업 횟수의 출처</t>
         </is>
       </c>
     </row>
@@ -1233,25 +1196,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>셋업 발생(분, 없으면 0)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>작업자</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>대기 사유(기계 바쁨/운반/자재/셋업/사람 없음)</t>
-        </is>
-      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>대기 사유(기계 바쁨/운반/자재/셋업/사람 없음/외주 대기)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>운반 수단</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>사진 파일</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1262,7 +1230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1286,14 +1254,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>하루 2~3회 전 구역을 돌며 기록. Little's law 검증과 버퍼 용량 추정용</t>
+          <t>【검증 전용, 모델 입력 아님】 하루 3회 전 구역을 돌며 기록 → Little's law·WIP 검증(시트 18). 버퍼 **용량**(최대 수용)은 시트 2 버퍼 용량 열에 입력</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>회차(09/13/16시)</t>
+          <t>회차(09:40/13:00/16:30)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1328,7 +1296,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>대기 사유</t>
+          <t>대기 사유(기계 바쁨/운반/자재/외주 대기/시공 대기)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1347,7 +1315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1412,6 +1380,67 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>반장·사장 인터뷰에서 '만약 ~면 ~한다' 형식으로 받아 적는다. 이 시트가 비어 있으면 모델은 '이상 공장'이 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>주제(배치구성/투입/기계선택/셋업시점/운반/잔업/급한주문/조립착수/품질판정/인력대체)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>만약 (조건)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>그러면 (행동)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>말한 사람</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>모델 반영(규칙 코드)</t>
         </is>
       </c>
     </row>
@@ -1440,39 +1469,39 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>반장·사장 인터뷰에서 '만약 ~면 ~한다' 형식으로 받아 적는다. 이 시트가 비어 있으면 모델은 '이상 공장'이 된다</t>
+          <t>13:00~15:00 3분 간격, 전 작업자. 가동률·재배치 근거</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>주제(배치구성/투입/기계선택/셋업시점/운반/잔업/급한주문/조립착수/품질판정/인력대체)</t>
+          <t>시각</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>만약 (조건)</t>
+          <t>작업자ID</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>그러면 (행동)</t>
+          <t>상태(가공/핸들링/보행/대기/셋업/부재)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>예외</t>
+          <t>위치(기계ID)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>말한 사람</t>
+          <t>대기 사유</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>모델 반영(규칙 코드)</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1482,67 +1511,6 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>13:00~15:00 3분 간격, 전 작업자. 가동률·재배치 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>시각</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>작업자ID</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>상태(가공/핸들링/보행/대기/셋업/부재)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>위치(기계ID)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>대기 사유</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1564,7 +1532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>03_공장복제_명세서 §1.2. 입력에 쓰지 않은 데이터로만 검증</t>
+          <t>【명세서 §1.2 표가 유일한 기준】 변환기가 이 시트를 factory.json observations.validation 으로 내보내고 sim/validate.py 가 판정. 입력에 쓰지 않은 데이터로만 검증</t>
         </is>
       </c>
     </row>
@@ -1576,32 +1544,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>모델 KPI 키(kpis.json 경로)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>실제 값</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>허용 오차</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>모델 값</t>
+          <t>허용 오차 % (v0.5)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>차이</t>
+          <t>허용 오차 절대값(비율형)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>단계(v0.5/v1)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1613,126 +1581,187 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>일/주 출하량(제품별)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>출하일지</t>
-        </is>
-      </c>
+          <t>2주 출하량(제품 수)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>products_completed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>±10%</t>
+          <t>출하장·세금계산서</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>추적 배치 리드타임</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>13_배치추적</t>
-        </is>
-      </c>
+          <t>생산 리드타임 평균(작업시간 분)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lead_time_work_min_avg</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>±15%</t>
+          <t>13_배치추적·2주 양식</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>시각별 구역 WIP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>14_WIP센서스</t>
-        </is>
-      </c>
+          <t>납기준수율(비율)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>on_time_ratio</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>±20%</t>
+          <t>시공캘린더 vs 상차</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>기계별 가동률</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CT 로그/워크샘플링</t>
-        </is>
-      </c>
+          <t>평균 WIP(배치)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avg_wip_batches</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>±10%p</t>
+          <t>14_WIP센서스·카메라</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>병목 앞 평균 대기열</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>센서스/영상</t>
-        </is>
-      </c>
+          <t>병목 1위 스테이션(ID)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bottleneck_ranking.0.station</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>순위 일치</t>
+          <t>센서스·카메라·CT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>게이트별 시간당 통과</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>15_게이트카운트</t>
-        </is>
-      </c>
+          <t>기계 가동률(예: EB1)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stations.EB1.utilization</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>±20%</t>
+          <t>CT 로그 2주</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>일 kWh / 최대수요 kW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>고지서/파워플래너</t>
-        </is>
-      </c>
+          <t>전력 2주 합계(kWh)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>energy.total_kwh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>±10% / ±15%</t>
+          <t>3EM/고지서 환산</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>v0.5</t>
         </is>
       </c>
     </row>
@@ -1743,14 +1772,104 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>반장 기록</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>±1회</t>
+          <t>13 양식 셋업 열·CT 간격</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>v0.5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기계를 '못 옮기는 진짜 이유'. 집진 메인 덕트 경로·드롭 지름, 공압 링메인·드롭, 3상 드롭, 바닥 하중·피트, 독 높이·문 폭, 피난 통로, 도장부스 방폭 구역, 덕트 아래 유효 천장고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>제약ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>종류(집진덕트/공압배관/분전반/바닥하중/피트·기초/독·문/소방피난/부스방폭/크레인/기둥/천장고)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>위치 x</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>위치 y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>범위·치수(지름 mm, 폭 m, 높이 m)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>연결 기계ID</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>이동 가능(Y/N)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>이전 비용(만원, 추정)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>근거(사진/설비담당)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1838,92 +1957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>기계를 '못 옮기는 진짜 이유'. 집진 메인 덕트 경로·드롭 지름, 공압 링메인·드롭, 3상 드롭, 바닥 하중·피트, 독 높이·문 폭, 피난 통로, 도장부스 방폭 구역, 덕트 아래 유효 천장고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>제약ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>종류(집진덕트/공압배관/분전반/바닥하중/피트·기초/독·문/소방피난/부스방폭/크레인/기둥/천장고)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>위치 x</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>위치 y</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>범위·치수(지름 mm, 폭 m, 높이 m)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>연결 기계ID</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>이동 가능(Y/N)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>이전 비용(만원, 추정)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>근거(사진/설비담당)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1937,6 +1971,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1954,50 +1989,116 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>적용 제품ID(쉼표)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>외주처</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>발주 시점(어느 공정 후·시공일 D-n)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>리드타임 min(일)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>합류 지점(조립/포장/시공현장)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>지연 시 조치(몸통 어디 적치)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>월 건수</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>지연 빈도(회/월)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>흐름 행렬. 기록 수량 × 관찰 라우팅 → 대차 단위. 거리는 직선이 아니라 통로 경로. 아래쪽 삼각 = 역류(backtracking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>From(구역/기계ID)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>To(구역/기계ID)</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>발주 시점(어느 공정 후·시공일 D-n)</t>
+          <t>대차/팔레트 이동 수(일)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>리드타임 min(일)</t>
+          <t>운반 수단</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>통로 거리(m, 통로 따라)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>합류 지점(조립/포장/시공현장)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>지연 시 조치(몸통 어디 적치)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>월 건수</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>지연 빈도(회/월)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2028,34 +2129,34 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>흐름 행렬. 기록 수량 × 관찰 라우팅 → 대차 단위. 거리는 직선이 아니라 통로 경로. 아래쪽 삼각 = 역류(backtracking)</t>
+          <t>SLP 활동관계도. X(격리)는 집진·도장부스·소음. A와 X는 각 5% 이내, U는 50% 안팎</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>From(구역/기계ID)</t>
+          <t>활동 i</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>To(구역/기계ID)</t>
+          <t>활동 j</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>대차/팔레트 이동 수(일)</t>
+          <t>근접도(A/E/I/O/U/X)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>운반 수단</t>
+          <t>이유코드(1흐름/2감독/3인원/4접촉/5편의/6공용설비/7서류/8소음·분진·화재/9서비스)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>통로 거리(m, 통로 따라)</t>
+          <t>말한 사람/관찰</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2075,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2084,42 +2185,66 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SLP 활동관계도. X(격리)는 집진·도장부스·소음. A와 X는 각 5% 이내, U는 50% 안팎</t>
+          <t>운반 자원과 출하·시공 용량. 변환기가 대차→handlers/cart_capacity, 지게차→forklifts 로 연결. 탑차·시공팀은 v1(출하 용량 제약)용 수집</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>활동 i</t>
+          <t>항목(대차/A형대차/팔레트/지게차/탑차/시공팀)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>활동 j</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>근접도(A/E/I/O/U/X)</t>
+          <t>적재량(부품 수 또는 현장 수)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>이유코드(1흐름/2감독/3인원/4접촉/5편의/6공용설비/7서류/8소음·분진·화재/9서비스)</t>
+          <t>속도(m/s) 또는 상차 시간(분/현장)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>말한 사람/관찰</t>
+          <t>담당(소유)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>운반 트리거(차면/호출/정시/직접)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>적재·하역 시간(분)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>빈 이동 비율(추정)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>하루 시공 가능 현장 수</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2568,6 +2693,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>스톱워치 측정. 병목 후보 스테이션당 당일 최소 10회(명세서 §4). 같은 측정#에 가공·핸들링을 여러 행으로 나눠 적으면 변환기가 측정# 단위로 합산한다. 평정은 ILO 100 기준, 첫 사이클은 호손 효과로 버림</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>기계ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>제품ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>부품명</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>측정#</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>부품/제품 치수(mm)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>엣지 변 수</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>홀 수</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>시작(HH:MM:SS)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>종료(HH:MM:SS)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>소요(초)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>구분(가공/핸들링/셋업/대기)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>평정(100=정상 속도)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>첫 사이클(버림 Y)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>영상 파일/타임코드</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2590,7 +2836,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>스톱워치 측정. 스테이션당 최소 5~10회. 핸들링(올리기/뒤집기/내리기)과 기계시간을 분리 기록. 삼각분포(min/mode/max) 도출용</t>
+          <t>제품 쌍(From→To)별 준비교체. 당일 1회 전과정 관찰 + 반장이 말하는 하루 횟수; 2차 방문에서 쌍별 3~5회. 변환기는 기계별 평균 소요·빈도를 setup_min 에 반영</t>
         </is>
       </c>
     </row>
@@ -2602,144 +2848,65 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>제품ID</t>
+          <t>From(제품/색상/두께)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>부품명</t>
+          <t>To(제품/색상/두께)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>측정#</t>
+          <t>전환 종류(엣지테이프/톱날/보링핀/도장색/프로그램)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>부품/제품 치수(mm)</t>
+          <t>시작</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>엣지 변 수</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>홀 수</t>
+          <t>소요(분)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>시작(HH:MM:SS)</t>
+          <t>내부/외부 요소 비율</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>종료(HH:MM:SS)</t>
+          <t>첫 양품까지(분)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>소요(초)</t>
+          <t>시험품 폐기(개)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>구분(가공/핸들링/셋업/대기)</t>
+          <t>빈도(회/일)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>작업자</t>
+          <t>작업자 수</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>영상 파일/타임코드</t>
+          <t>개선 아이디어(SMED)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>제품 전환 시 준비교체. 하루 발생 횟수도 반장에게 질문</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>기계ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>전환 내용(엣지테이프 색/두께, 보링 핀, 도장 색, 톱날)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>시작</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>종료</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>소요(분)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>빈도(회/일)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>작업자 수</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>개선 아이디어(SMED)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2841,7 +3008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2862,6 +3029,8 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2884,80 +3053,90 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>원장 색상</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>원장 두께(mm)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>월 수량</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>주문당 수량(배치)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>주문당 수량(배치, 평균; 분포는 시트 8)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>라우팅(cut&gt;edge&gt;bore&gt;finish&gt;dry&gt;assemble&gt;pack)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>부품명</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>수량/제품</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>가로 w(m)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>세로 d(m)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>두께 t(m)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>엣지 변 수</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>홀 수</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>도장(Y/N)</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>조립 시간(분/제품)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>포장 시간(분/제품)</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>판매가(원)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>

--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -2261,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2466,90 +2466,110 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
+          <t>이송속도 v_f(m/min, 엣지·샌더·런닝쏘)</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>부품 간격 G(m, 엣지)</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>부품당 통과 횟수(엣지 2~4)</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>리턴컨베이어(Y/N)</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
           <t>소정지 빈도(회/시간)</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>예열/청소 시간(분/일)</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>입력버퍼 x</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>입력버퍼 y</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>출력버퍼 x</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>출력버퍼 y</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>버퍼 용량(배치/대차 수)</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>셋업 시간(분)</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>셋업 트리거(색상/두께/제품)</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t>MTBF(시간)</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>MTTR(분)</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>불량률(%)</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>명판사진 파일</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
+      <c r="AV2" s="2" t="inlineStr">
         <is>
           <t>전체사진 파일</t>
         </is>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>HMI 사진</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="inlineStr">
+      <c r="AX2" s="2" t="inlineStr">
         <is>
           <t>PLC/HMI 브랜드</t>
         </is>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>네트워크 포트(Y/N)</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr">
+      <c r="AZ2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>

--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -30,6 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_from-to" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_REL관계도" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_운반_출하대장" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_카메라보정" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2255,6 +2256,139 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>카메라당 바닥 제어점 8~12개(근·중·원거리, 겹침 구역 포함, 레이저 측정) + 검증 보행(L자 경로, 보통/대차 속도, 지게차 루프). 홀드아웃 RMS 근 &lt;0.15 m, 원 &lt;0.4 m. 카메라를 건드리면 재보정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>카메라ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>설치 위치 x</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>높이(m)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>하향각(도)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>렌즈(mm)/화각</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>제어점#</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>제어점 바닥 x</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>제어점 바닥 y</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>이미지 u(px)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>이미지 v(px)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>검증보행 구간</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>실측 거리(m)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>추적 거리(m)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>실측 속도(m/s)</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>추적 속도(m/s)</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>P90 오차(m)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -1517,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1582,7 +1582,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2주 출하량(제품 수)</t>
+          <t>전체 기간 출하량(제품 수, 워밍업 포함)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1593,7 +1593,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>출하장·세금계산서</t>
+          <t>출하장·세금계산서(같은 기간)</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1772,7 +1772,11 @@
           <t>셋업 횟수/일</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>setups_per_day</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,6 +1788,60 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>생산 리드타임 P90(분)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lead_time_work_min_p90</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13 양식</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>v0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>정상상태 완료 제품 수(워밍업 제외 기간)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>products_completed_steady</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>출하장(같은 기간)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>v0.5</t>
         </is>
@@ -2847,7 +2905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2866,6 +2924,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2908,50 +2967,55 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>엣지 길이 합(m)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>홀 수</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>시작(HH:MM:SS)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>종료(HH:MM:SS)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>소요(초)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>구분(가공/핸들링/셋업/대기)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>평정(100=정상 속도)</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>첫 사이클(버림 Y)</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>작업자</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>영상 파일/타임코드</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>

--- a/factory-twin/capture/templates/현장수집_템플릿.xlsx
+++ b/factory-twin/capture/templates/현장수집_템플릿.xlsx
@@ -918,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -966,152 +966,159 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【필수】 당일 투입 현장 수 / 당일 출하 현장 수 (처리량 검증: 출하 = 투입 − ΔWIP)</t>
+          <t>【필수】 앞으로 2주(로깅 기간)가 평소보다 한가한가 바쁜가? 재공이 쌓이는 날이 3~4일은 있는가? (한가한 2주는 구조 검증에 무가치 — 연구 18)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>실측 → 도면 → 재단표 작성까지 보통 며칠? 누가? 도면 대기 건수?</t>
+          <t>【필수】 당일 투입 현장 수 / 당일 출하 현장 수 (처리량 검증: 출하 = 투입 − ΔWIP)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>탑차 수, 시공팀 수, 하루 시공 가능 현장 수, 상차 시간</t>
+          <t>실측 → 도면 → 재단표 작성까지 보통 며칠? 누가? 도면 대기 건수?</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>시공일이 바뀌거나 취소되는 일이 한 달에 몇 번? 현장에서 불량 발견해 급히 재제작하는 일은?</t>
+          <t>탑차 수, 시공팀 수, 하루 시공 가능 현장 수, 상차 시간</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>주력 제품군과 월 생산량</t>
+          <t>시공일이 바뀌거나 취소되는 일이 한 달에 몇 번? 현장에서 불량 발견해 급히 재제작하는 일은?</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>주문 방식(수주/재고), 평균 리드타임</t>
+          <t>주력 제품군과 월 생산량</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>공정 순서와 병목(왜)</t>
+          <t>주문 방식(수주/재고), 평균 리드타임</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기계별 하루 가동시간/잔업/특근</t>
+          <t>공정 순서와 병목(왜)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가장 자주 바뀌는 세팅과 교체 시간</t>
+          <t>기계별 하루 가동시간/잔업/특근</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WIP 적치 위치와 대차/랙 수</t>
+          <t>가장 자주 바뀌는 세팅과 교체 시간</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>지게차/대차 대수, 경로, 하루 이동 횟수</t>
+          <t>WIP 적치 위치와 대차/랙 수</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>불량/재작업 비율과 원인</t>
+          <t>지게차/대차 대수, 경로, 하루 이동 횟수</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>집진기/컴프레서 가동 패턴</t>
+          <t>불량/재작업 비율과 원인</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>월 전기요금, 계약전력, 피크</t>
+          <t>집진기/컴프레서 가동 패턴</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ERP/MES/엑셀 기록 형식</t>
+          <t>월 전기요금, 계약전력, 피크</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>안전/촬영 금지 구역</t>
+          <t>ERP/MES/엑셀 기록 형식</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>향후 설비/레이아웃 변경 계획</t>
+          <t>안전/촬영 금지 구역</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>작업자 수, 숙련 구분, 외국인 비율</t>
+          <t>향후 설비/레이아웃 변경 계획</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>올해 가장 비쌌던 비용</t>
+          <t>작업자 수, 숙련 구분, 외국인 비율</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>납기 지연 횟수와 손해</t>
+          <t>올해 가장 비쌌던 비용</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>사고 싶은 기계와 망설이는 이유</t>
+          <t>납기 지연 횟수와 손해</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>사고 싶은 기계와 망설이는 이유</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>정부 스마트공장 사업 수혜 이력</t>
         </is>
@@ -1128,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1145,6 +1152,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1217,10 +1227,25 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>부품 수(입/출)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>함께 처리한 배치(같은 원판·셋업)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>외주 반출/반입 시각</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
           <t>사진 파일</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1395,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1404,6 +1429,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1421,25 +1450,45 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>만약 (조건)</t>
+          <t>트리거(언제 결정: 아침 계획/대기열 변화/카트 참/전화)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>만약 (조건 변수·비교값)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>그러면 (행동)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>예외</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>우선순위(1=최상위 예외, 큰 수=평상시)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>말한 사람</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>근거 사례(주문ID·날짜)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>기록 지지(rule_fit: n/N)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>모델 반영(규칙 코드)</t>
         </is>
@@ -3141,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3154,6 +3203,8 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3210,6 +3261,16 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>배치 규칙(고정/순환/응원·어디로)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>근속 3개월 미만(Y)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
